--- a/R/data/APT_data-info-dictionary_final-7.5.25.xlsx
+++ b/R/data/APT_data-info-dictionary_final-7.5.25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asspreventiontorture.sharepoint.com/sites/Operations/Data/PROJECTS/Visualization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="932" documentId="8_{9E7471CC-608F-448E-A4AD-63013E2489A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{675FFBDF-8F1D-4E19-B5AF-907377ED0A70}"/>
+  <xr:revisionPtr revIDLastSave="1034" documentId="8_{9E7471CC-608F-448E-A4AD-63013E2489A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3C30D29-3021-42D8-8A8D-7BBD6B756C67}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="63735" yWindow="6945" windowWidth="14310" windowHeight="8145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data revised 25.09" sheetId="1" r:id="rId1"/>
@@ -735,6 +735,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t>Torture is an attack on a person’s humanity and dignity. It is a grievous violation of human rights that is absolutely prohibited and cannot be justified under any circumstances</t>
     </r>
@@ -878,6 +879,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">In 1984, the Member States of the United Nations (UN) adopted the Convention against Torture and Other Cruel, Inhuman or Degrading Treatment or Punishment (hereafter referred to as the Convention against Torture). They sought to provide the world with a robust international treaty that would reaffirm the absolute prohibition of torture under any circumstances. </t>
     </r>
@@ -928,6 +930,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Under international law, </t>
     </r>
@@ -954,6 +957,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">The Committee against Torture </t>
     </r>
@@ -983,6 +987,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">One of the functions of the UN Committee Against Tortures is to review States’ progress on the implementation of the Convention Against Torture. As part of this review process, the </t>
     </r>
@@ -1024,6 +1029,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">The Constitution of a country is </t>
     </r>
@@ -1060,6 +1066,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Domestic law refers to any law or regulation adopted by a state, being applicable all over its territory. </t>
     </r>
@@ -1091,6 +1098,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">The States parties to the Optional Protocol have the obligation to establish independent institutions, which </t>
     </r>
@@ -1169,6 +1177,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">National human rights institutions (NHRIs) are State bodies with the mandate to </t>
     </r>
@@ -1207,6 +1216,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Quattrocento Sans"/>
+        <family val="2"/>
       </rPr>
       <t>In 1993, the UN General Assembly adopted the Paris Principles, which require NHRIs to be fully </t>
     </r>
@@ -1345,6 +1355,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1355,6 +1366,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1373,11 +1385,13 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1431,7 +1445,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1520,6 +1534,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFDBE9F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -1685,7 +1705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1861,6 +1881,9 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2084,13 +2107,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1577"/>
+  <dimension ref="A1:E1577"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.36328125" customWidth="1"/>
     <col min="2" max="2" width="28.6328125" customWidth="1"/>
     <col min="3" max="3" width="90.6328125" customWidth="1"/>
-    <col min="4" max="26" width="8.6328125" customWidth="1"/>
+    <col min="4" max="20" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.5">
@@ -5315,7 +5338,7 @@
         <v>37622</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="15.75" customHeight="1">
+    <row r="193" spans="1:5" ht="15.75" customHeight="1">
       <c r="A193" s="4" t="s">
         <v>162</v>
       </c>
@@ -5330,7 +5353,7 @@
       </c>
       <c r="E193" s="10"/>
     </row>
-    <row r="194" spans="1:6" ht="15.75" customHeight="1">
+    <row r="194" spans="1:5" ht="15.75" customHeight="1">
       <c r="A194" s="4" t="s">
         <v>162</v>
       </c>
@@ -5347,7 +5370,7 @@
         <v>36161</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="15.75" customHeight="1">
+    <row r="195" spans="1:5" ht="15.75" customHeight="1">
       <c r="A195" s="4" t="s">
         <v>162</v>
       </c>
@@ -5364,7 +5387,7 @@
         <v>45489</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="15.75" customHeight="1">
+    <row r="196" spans="1:5" ht="15.75" customHeight="1">
       <c r="A196" s="4" t="s">
         <v>162</v>
       </c>
@@ -5381,7 +5404,7 @@
         <v>34700</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="15.75" customHeight="1">
+    <row r="197" spans="1:5" ht="15.75" customHeight="1">
       <c r="A197" s="4" t="s">
         <v>162</v>
       </c>
@@ -5398,7 +5421,7 @@
         <v>40544</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="15.75" customHeight="1">
+    <row r="198" spans="1:5" ht="15.75" customHeight="1">
       <c r="A198" s="13" t="s">
         <v>162</v>
       </c>
@@ -5415,7 +5438,7 @@
         <v>42005</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="15.75" customHeight="1">
+    <row r="199" spans="1:5" ht="15.75" customHeight="1">
       <c r="A199" s="14" t="s">
         <v>5</v>
       </c>
@@ -5429,12 +5452,8 @@
         <v>12</v>
       </c>
       <c r="E199" s="17"/>
-      <c r="F199">
-        <f>COUNTIF(D199:D395, "Yes")</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" ht="15.75" customHeight="1">
+    </row>
+    <row r="200" spans="1:5" ht="15.75" customHeight="1">
       <c r="A200" s="14" t="s">
         <v>5</v>
       </c>
@@ -5451,7 +5470,7 @@
         <v>37987</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="15.75" customHeight="1">
+    <row r="201" spans="1:5" ht="15.75" customHeight="1">
       <c r="A201" s="14" t="s">
         <v>5</v>
       </c>
@@ -5466,7 +5485,7 @@
       </c>
       <c r="E201" s="17"/>
     </row>
-    <row r="202" spans="1:6" ht="15.75" customHeight="1">
+    <row r="202" spans="1:5" ht="15.75" customHeight="1">
       <c r="A202" s="14" t="s">
         <v>5</v>
       </c>
@@ -5481,7 +5500,7 @@
       </c>
       <c r="E202" s="17"/>
     </row>
-    <row r="203" spans="1:6" ht="15.75" customHeight="1">
+    <row r="203" spans="1:5" ht="15.75" customHeight="1">
       <c r="A203" s="14" t="s">
         <v>5</v>
       </c>
@@ -5498,7 +5517,7 @@
         <v>42005</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="15.75" customHeight="1">
+    <row r="204" spans="1:5" ht="15.75" customHeight="1">
       <c r="A204" s="14" t="s">
         <v>5</v>
       </c>
@@ -5515,7 +5534,7 @@
         <v>38718</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="15.5" customHeight="1">
+    <row r="205" spans="1:5" ht="15.5" customHeight="1">
       <c r="A205" s="14" t="s">
         <v>5</v>
       </c>
@@ -5532,7 +5551,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="15.75" customHeight="1">
+    <row r="206" spans="1:5" ht="15.75" customHeight="1">
       <c r="A206" s="14" t="s">
         <v>5</v>
       </c>
@@ -5547,7 +5566,7 @@
       </c>
       <c r="E206" s="17"/>
     </row>
-    <row r="207" spans="1:6" ht="15.75" customHeight="1">
+    <row r="207" spans="1:5" ht="15.75" customHeight="1">
       <c r="A207" s="14" t="s">
         <v>5</v>
       </c>
@@ -5564,7 +5583,7 @@
         <v>39448</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="15.75" customHeight="1">
+    <row r="208" spans="1:5" ht="15.75" customHeight="1">
       <c r="A208" s="14" t="s">
         <v>5</v>
       </c>
@@ -8395,7 +8414,7 @@
       </c>
       <c r="E384" s="21"/>
     </row>
-    <row r="385" spans="1:8" ht="15.75" customHeight="1">
+    <row r="385" spans="1:5" ht="15.75" customHeight="1">
       <c r="A385" s="14" t="s">
         <v>162</v>
       </c>
@@ -8410,7 +8429,7 @@
       </c>
       <c r="E385" s="21"/>
     </row>
-    <row r="386" spans="1:8" ht="15.75" customHeight="1">
+    <row r="386" spans="1:5" ht="15.75" customHeight="1">
       <c r="A386" s="14" t="s">
         <v>162</v>
       </c>
@@ -8427,7 +8446,7 @@
         <v>42736</v>
       </c>
     </row>
-    <row r="387" spans="1:8" ht="15.75" customHeight="1">
+    <row r="387" spans="1:5" ht="15.75" customHeight="1">
       <c r="A387" s="14" t="s">
         <v>162</v>
       </c>
@@ -8442,7 +8461,7 @@
       </c>
       <c r="E387" s="21"/>
     </row>
-    <row r="388" spans="1:8" ht="15.75" customHeight="1">
+    <row r="388" spans="1:5" ht="15.75" customHeight="1">
       <c r="A388" s="14" t="s">
         <v>162</v>
       </c>
@@ -8457,7 +8476,7 @@
       </c>
       <c r="E388" s="21"/>
     </row>
-    <row r="389" spans="1:8" ht="15.75" customHeight="1">
+    <row r="389" spans="1:5" ht="15.75" customHeight="1">
       <c r="A389" s="14" t="s">
         <v>162</v>
       </c>
@@ -8472,7 +8491,7 @@
       </c>
       <c r="E389" s="21"/>
     </row>
-    <row r="390" spans="1:8" ht="15.75" customHeight="1">
+    <row r="390" spans="1:5" ht="15.75" customHeight="1">
       <c r="A390" s="14" t="s">
         <v>162</v>
       </c>
@@ -8487,7 +8506,7 @@
       </c>
       <c r="E390" s="21"/>
     </row>
-    <row r="391" spans="1:8" ht="15.75" customHeight="1">
+    <row r="391" spans="1:5" ht="15.75" customHeight="1">
       <c r="A391" s="14" t="s">
         <v>162</v>
       </c>
@@ -8502,7 +8521,7 @@
       </c>
       <c r="E391" s="21"/>
     </row>
-    <row r="392" spans="1:8" ht="15.75" customHeight="1">
+    <row r="392" spans="1:5" ht="15.75" customHeight="1">
       <c r="A392" s="14" t="s">
         <v>162</v>
       </c>
@@ -8517,7 +8536,7 @@
       </c>
       <c r="E392" s="21"/>
     </row>
-    <row r="393" spans="1:8" ht="15.75" customHeight="1">
+    <row r="393" spans="1:5" ht="15.75" customHeight="1">
       <c r="A393" s="14" t="s">
         <v>162</v>
       </c>
@@ -8532,7 +8551,7 @@
       </c>
       <c r="E393" s="21"/>
     </row>
-    <row r="394" spans="1:8" ht="15.75" customHeight="1">
+    <row r="394" spans="1:5" ht="15.75" customHeight="1">
       <c r="A394" s="14" t="s">
         <v>162</v>
       </c>
@@ -8547,7 +8566,7 @@
       </c>
       <c r="E394" s="21"/>
     </row>
-    <row r="395" spans="1:8" ht="15.75" customHeight="1">
+    <row r="395" spans="1:5" ht="15.75" customHeight="1">
       <c r="A395" s="24" t="s">
         <v>162</v>
       </c>
@@ -8562,7 +8581,7 @@
       </c>
       <c r="E395" s="21"/>
     </row>
-    <row r="396" spans="1:8" ht="15.75" customHeight="1">
+    <row r="396" spans="1:5" ht="15.75" customHeight="1">
       <c r="A396" s="25" t="s">
         <v>5</v>
       </c>
@@ -8577,7 +8596,7 @@
       </c>
       <c r="E396" s="28"/>
     </row>
-    <row r="397" spans="1:8" ht="15.75" customHeight="1">
+    <row r="397" spans="1:5" ht="15.75" customHeight="1">
       <c r="A397" s="25" t="s">
         <v>5</v>
       </c>
@@ -8594,7 +8613,7 @@
         <v>33604</v>
       </c>
     </row>
-    <row r="398" spans="1:8" ht="15.75" customHeight="1">
+    <row r="398" spans="1:5" ht="15.75" customHeight="1">
       <c r="A398" s="25" t="s">
         <v>5</v>
       </c>
@@ -8609,7 +8628,7 @@
       </c>
       <c r="E398" s="28"/>
     </row>
-    <row r="399" spans="1:8" ht="15.75" customHeight="1">
+    <row r="399" spans="1:5" ht="15.75" customHeight="1">
       <c r="A399" s="25" t="s">
         <v>5</v>
       </c>
@@ -8624,7 +8643,7 @@
       </c>
       <c r="E399" s="28"/>
     </row>
-    <row r="400" spans="1:8" ht="15.75" customHeight="1">
+    <row r="400" spans="1:5" ht="15.75" customHeight="1">
       <c r="A400" s="25" t="s">
         <v>5</v>
       </c>
@@ -8638,10 +8657,6 @@
         <v>12</v>
       </c>
       <c r="E400" s="28"/>
-      <c r="H400">
-        <f>COUNTIF(D396:D592, "Yes")</f>
-        <v>141</v>
-      </c>
     </row>
     <row r="401" spans="1:5" ht="15.75" customHeight="1">
       <c r="A401" s="25" t="s">
@@ -11803,7 +11818,7 @@
         <v>42736</v>
       </c>
     </row>
-    <row r="593" spans="1:7" ht="15.75" customHeight="1">
+    <row r="593" spans="1:5" ht="15.75" customHeight="1">
       <c r="A593" s="34" t="s">
         <v>5</v>
       </c>
@@ -11820,7 +11835,7 @@
         <v>30682</v>
       </c>
     </row>
-    <row r="594" spans="1:7" ht="15.75" customHeight="1">
+    <row r="594" spans="1:5" ht="15.75" customHeight="1">
       <c r="A594" s="34" t="s">
         <v>5</v>
       </c>
@@ -11836,12 +11851,8 @@
       <c r="E594" s="37">
         <v>30682</v>
       </c>
-      <c r="G594">
-        <f>COUNTIF(D593:D789, "Yes")</f>
-        <v>167</v>
-      </c>
-    </row>
-    <row r="595" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="595" spans="1:5" ht="15.75" customHeight="1">
       <c r="A595" s="34" t="s">
         <v>5</v>
       </c>
@@ -11858,7 +11869,7 @@
         <v>30682</v>
       </c>
     </row>
-    <row r="596" spans="1:7" ht="15.75" customHeight="1">
+    <row r="596" spans="1:5" ht="15.75" customHeight="1">
       <c r="A596" s="34" t="s">
         <v>5</v>
       </c>
@@ -11875,7 +11886,7 @@
         <v>39083</v>
       </c>
     </row>
-    <row r="597" spans="1:7" ht="15.75" customHeight="1">
+    <row r="597" spans="1:5" ht="15.75" customHeight="1">
       <c r="A597" s="34" t="s">
         <v>5</v>
       </c>
@@ -11892,7 +11903,7 @@
         <v>40544</v>
       </c>
     </row>
-    <row r="598" spans="1:7" ht="15.75" customHeight="1">
+    <row r="598" spans="1:5" ht="15.75" customHeight="1">
       <c r="A598" s="34" t="s">
         <v>5</v>
       </c>
@@ -11909,7 +11920,7 @@
         <v>39814</v>
       </c>
     </row>
-    <row r="599" spans="1:7" ht="15.75" customHeight="1">
+    <row r="599" spans="1:5" ht="15.75" customHeight="1">
       <c r="A599" s="34" t="s">
         <v>5</v>
       </c>
@@ -11926,7 +11937,7 @@
         <v>32143</v>
       </c>
     </row>
-    <row r="600" spans="1:7" ht="15.75" customHeight="1">
+    <row r="600" spans="1:5" ht="15.75" customHeight="1">
       <c r="A600" s="34" t="s">
         <v>5</v>
       </c>
@@ -11943,7 +11954,7 @@
         <v>36924</v>
       </c>
     </row>
-    <row r="601" spans="1:7" ht="15.75" customHeight="1">
+    <row r="601" spans="1:5" ht="15.75" customHeight="1">
       <c r="A601" s="34" t="s">
         <v>5</v>
       </c>
@@ -11960,7 +11971,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="602" spans="1:7" ht="15.75" customHeight="1">
+    <row r="602" spans="1:5" ht="15.75" customHeight="1">
       <c r="A602" s="34" t="s">
         <v>5</v>
       </c>
@@ -11977,7 +11988,7 @@
         <v>34700</v>
       </c>
     </row>
-    <row r="603" spans="1:7" ht="15.75" customHeight="1">
+    <row r="603" spans="1:5" ht="15.75" customHeight="1">
       <c r="A603" s="34" t="s">
         <v>5</v>
       </c>
@@ -11994,7 +12005,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="604" spans="1:7" ht="15.75" customHeight="1">
+    <row r="604" spans="1:5" ht="15.75" customHeight="1">
       <c r="A604" s="34" t="s">
         <v>5</v>
       </c>
@@ -12011,7 +12022,7 @@
         <v>43475</v>
       </c>
     </row>
-    <row r="605" spans="1:7" ht="15.75" customHeight="1">
+    <row r="605" spans="1:5" ht="15.75" customHeight="1">
       <c r="A605" s="34" t="s">
         <v>5</v>
       </c>
@@ -12028,7 +12039,7 @@
         <v>33239</v>
       </c>
     </row>
-    <row r="606" spans="1:7" ht="15.75" customHeight="1">
+    <row r="606" spans="1:5" ht="15.75" customHeight="1">
       <c r="A606" s="34" t="s">
         <v>5</v>
       </c>
@@ -12045,7 +12056,7 @@
         <v>42005</v>
       </c>
     </row>
-    <row r="607" spans="1:7" ht="15.75" customHeight="1">
+    <row r="607" spans="1:5" ht="15.75" customHeight="1">
       <c r="A607" s="34" t="s">
         <v>5</v>
       </c>
@@ -12062,7 +12073,7 @@
         <v>39448</v>
       </c>
     </row>
-    <row r="608" spans="1:7" ht="15.75" customHeight="1">
+    <row r="608" spans="1:5" ht="15.75" customHeight="1">
       <c r="A608" s="34" t="s">
         <v>5</v>
       </c>
@@ -15013,7 +15024,7 @@
       </c>
       <c r="E784" s="40"/>
     </row>
-    <row r="785" spans="1:7" ht="15.75" customHeight="1">
+    <row r="785" spans="1:5" ht="15.75" customHeight="1">
       <c r="A785" s="34" t="s">
         <v>162</v>
       </c>
@@ -15030,7 +15041,7 @@
         <v>39448</v>
       </c>
     </row>
-    <row r="786" spans="1:7" ht="15.75" customHeight="1">
+    <row r="786" spans="1:5" ht="15.75" customHeight="1">
       <c r="A786" s="34" t="s">
         <v>162</v>
       </c>
@@ -15047,7 +15058,7 @@
         <v>31413</v>
       </c>
     </row>
-    <row r="787" spans="1:7" ht="15.75" customHeight="1">
+    <row r="787" spans="1:5" ht="15.75" customHeight="1">
       <c r="A787" s="34" t="s">
         <v>162</v>
       </c>
@@ -15064,7 +15075,7 @@
         <v>33604</v>
       </c>
     </row>
-    <row r="788" spans="1:7" ht="15.75" customHeight="1">
+    <row r="788" spans="1:5" ht="15.75" customHeight="1">
       <c r="A788" s="34" t="s">
         <v>162</v>
       </c>
@@ -15079,7 +15090,7 @@
       </c>
       <c r="E788" s="40"/>
     </row>
-    <row r="789" spans="1:7" ht="15.75" customHeight="1">
+    <row r="789" spans="1:5" ht="15.75" customHeight="1">
       <c r="A789" s="44" t="s">
         <v>162</v>
       </c>
@@ -15096,7 +15107,7 @@
         <v>34335</v>
       </c>
     </row>
-    <row r="790" spans="1:7" ht="15.75" customHeight="1">
+    <row r="790" spans="1:5" ht="15.75" customHeight="1">
       <c r="A790" s="45" t="s">
         <v>5</v>
       </c>
@@ -15112,12 +15123,8 @@
       <c r="E790" s="48">
         <v>33970</v>
       </c>
-      <c r="G790">
-        <f>COUNTIF(D790:D986,"Partially")</f>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="791" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="791" spans="1:5" ht="15.75" customHeight="1">
       <c r="A791" s="45" t="s">
         <v>5</v>
       </c>
@@ -15134,7 +15141,7 @@
         <v>30682</v>
       </c>
     </row>
-    <row r="792" spans="1:7" ht="15.75" customHeight="1">
+    <row r="792" spans="1:5" ht="15.75" customHeight="1">
       <c r="A792" s="45" t="s">
         <v>5</v>
       </c>
@@ -15151,7 +15158,7 @@
         <v>36892</v>
       </c>
     </row>
-    <row r="793" spans="1:7" ht="15.75" customHeight="1">
+    <row r="793" spans="1:5" ht="15.75" customHeight="1">
       <c r="A793" s="45" t="s">
         <v>5</v>
       </c>
@@ -15166,7 +15173,7 @@
       </c>
       <c r="E793" s="48"/>
     </row>
-    <row r="794" spans="1:7" ht="15.75" customHeight="1">
+    <row r="794" spans="1:5" ht="15.75" customHeight="1">
       <c r="A794" s="45" t="s">
         <v>5</v>
       </c>
@@ -15183,7 +15190,7 @@
         <v>40544</v>
       </c>
     </row>
-    <row r="795" spans="1:7" ht="15.75" customHeight="1">
+    <row r="795" spans="1:5" ht="15.75" customHeight="1">
       <c r="A795" s="45" t="s">
         <v>5</v>
       </c>
@@ -15200,7 +15207,7 @@
         <v>35431</v>
       </c>
     </row>
-    <row r="796" spans="1:7" s="103" customFormat="1" ht="15.75" customHeight="1">
+    <row r="796" spans="1:5" s="103" customFormat="1" ht="15.75" customHeight="1">
       <c r="A796" s="121" t="s">
         <v>5</v>
       </c>
@@ -15217,7 +15224,7 @@
         <v>35431</v>
       </c>
     </row>
-    <row r="797" spans="1:7" ht="15.75" customHeight="1">
+    <row r="797" spans="1:5" ht="15.75" customHeight="1">
       <c r="A797" s="45" t="s">
         <v>5</v>
       </c>
@@ -15234,7 +15241,7 @@
         <v>31048</v>
       </c>
     </row>
-    <row r="798" spans="1:7" ht="15.75" customHeight="1">
+    <row r="798" spans="1:5" ht="15.75" customHeight="1">
       <c r="A798" s="45" t="s">
         <v>5</v>
       </c>
@@ -15251,7 +15258,7 @@
         <v>30682</v>
       </c>
     </row>
-    <row r="799" spans="1:7" ht="15.75" customHeight="1">
+    <row r="799" spans="1:5" ht="15.75" customHeight="1">
       <c r="A799" s="45" t="s">
         <v>5</v>
       </c>
@@ -15268,7 +15275,7 @@
         <v>30682</v>
       </c>
     </row>
-    <row r="800" spans="1:7" ht="15.75" customHeight="1">
+    <row r="800" spans="1:5" ht="15.75" customHeight="1">
       <c r="A800" s="45" t="s">
         <v>5</v>
       </c>
@@ -16153,10 +16160,12 @@
       <c r="C853" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D853" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E853" s="48"/>
+      <c r="D853" s="141" t="s">
+        <v>213</v>
+      </c>
+      <c r="E853" s="142">
+        <v>37065</v>
+      </c>
     </row>
     <row r="854" spans="1:5" ht="15.75" customHeight="1">
       <c r="A854" s="45" t="s">
@@ -16185,10 +16194,12 @@
       <c r="C855" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D855" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E855" s="48"/>
+      <c r="D855" s="141" t="s">
+        <v>213</v>
+      </c>
+      <c r="E855" s="142">
+        <v>42192</v>
+      </c>
     </row>
     <row r="856" spans="1:5" ht="15.75" customHeight="1">
       <c r="A856" s="45" t="s">
@@ -16207,7 +16218,7 @@
         <v>43101</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="15.75" customHeight="1">
+    <row r="857" spans="1:5" ht="15.5" customHeight="1">
       <c r="A857" s="45" t="s">
         <v>44</v>
       </c>
@@ -16292,7 +16303,7 @@
         <v>36161</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="15.75" customHeight="1">
+    <row r="862" spans="1:5" ht="15.5" customHeight="1">
       <c r="A862" s="45" t="s">
         <v>44</v>
       </c>
@@ -16888,14 +16899,14 @@
       <c r="C898" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D898" s="47" t="s">
-        <v>213</v>
+      <c r="D898" s="141" t="s">
+        <v>8</v>
       </c>
       <c r="E898" s="48">
         <v>43831</v>
       </c>
     </row>
-    <row r="899" spans="1:5" ht="15.75" customHeight="1">
+    <row r="899" spans="1:5" ht="15.5" customHeight="1">
       <c r="A899" s="45" t="s">
         <v>95</v>
       </c>
@@ -16905,8 +16916,8 @@
       <c r="C899" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D899" s="47" t="s">
-        <v>213</v>
+      <c r="D899" s="143" t="s">
+        <v>8</v>
       </c>
       <c r="E899" s="48">
         <v>43466</v>
@@ -17005,10 +17016,12 @@
       <c r="C905" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D905" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E905" s="48"/>
+      <c r="D905" s="141" t="s">
+        <v>8</v>
+      </c>
+      <c r="E905" s="124">
+        <v>39995</v>
+      </c>
     </row>
     <row r="906" spans="1:5" ht="15.5" customHeight="1">
       <c r="A906" s="45" t="s">
@@ -17037,8 +17050,8 @@
       <c r="C907" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D907" s="47" t="s">
-        <v>213</v>
+      <c r="D907" s="141" t="s">
+        <v>8</v>
       </c>
       <c r="E907" s="48">
         <v>40909</v>
@@ -17154,8 +17167,8 @@
       <c r="C914" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D914" s="47" t="s">
-        <v>213</v>
+      <c r="D914" s="141" t="s">
+        <v>8</v>
       </c>
       <c r="E914" s="48">
         <v>44197</v>
@@ -17188,8 +17201,8 @@
       <c r="C916" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D916" s="47" t="s">
-        <v>213</v>
+      <c r="D916" s="141" t="s">
+        <v>8</v>
       </c>
       <c r="E916" s="48">
         <v>39448</v>
@@ -17342,7 +17355,7 @@
       </c>
       <c r="E925" s="48"/>
     </row>
-    <row r="926" spans="1:5" ht="15.75" customHeight="1">
+    <row r="926" spans="1:5" ht="15.5" customHeight="1">
       <c r="A926" s="45" t="s">
         <v>143</v>
       </c>
@@ -17503,8 +17516,8 @@
       <c r="C935" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D935" s="47" t="s">
-        <v>213</v>
+      <c r="D935" s="143" t="s">
+        <v>8</v>
       </c>
       <c r="E935" s="48">
         <v>41640</v>
@@ -17588,10 +17601,12 @@
       <c r="C940" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D940" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E940" s="48"/>
+      <c r="D940" s="141" t="s">
+        <v>213</v>
+      </c>
+      <c r="E940" s="142">
+        <v>34335</v>
+      </c>
     </row>
     <row r="941" spans="1:5" ht="15.75" customHeight="1">
       <c r="A941" s="45" t="s">
@@ -17789,7 +17804,7 @@
       </c>
       <c r="E952" s="48"/>
     </row>
-    <row r="953" spans="1:5" ht="15.75" customHeight="1">
+    <row r="953" spans="1:5" ht="15.5" customHeight="1">
       <c r="A953" s="45" t="s">
         <v>162</v>
       </c>
@@ -17882,10 +17897,12 @@
       <c r="C958" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D958" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E958" s="48"/>
+      <c r="D958" s="123" t="s">
+        <v>213</v>
+      </c>
+      <c r="E958" s="124">
+        <v>42925</v>
+      </c>
     </row>
     <row r="959" spans="1:5" ht="15.75" customHeight="1">
       <c r="A959" s="45" t="s">
@@ -18172,12 +18189,14 @@
       <c r="C976" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D976" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E976" s="48"/>
-    </row>
-    <row r="977" spans="1:6" ht="15.75" customHeight="1">
+      <c r="D976" s="141" t="s">
+        <v>213</v>
+      </c>
+      <c r="E976" s="142">
+        <v>44229</v>
+      </c>
+    </row>
+    <row r="977" spans="1:5" ht="15.75" customHeight="1">
       <c r="A977" s="45" t="s">
         <v>162</v>
       </c>
@@ -18194,7 +18213,7 @@
         <v>30682</v>
       </c>
     </row>
-    <row r="978" spans="1:6" ht="15.75" customHeight="1">
+    <row r="978" spans="1:5" ht="15.75" customHeight="1">
       <c r="A978" s="45" t="s">
         <v>162</v>
       </c>
@@ -18211,7 +18230,7 @@
         <v>40909</v>
       </c>
     </row>
-    <row r="979" spans="1:6" ht="15.75" customHeight="1">
+    <row r="979" spans="1:5" ht="15.75" customHeight="1">
       <c r="A979" s="45" t="s">
         <v>162</v>
       </c>
@@ -18228,7 +18247,7 @@
         <v>44562</v>
       </c>
     </row>
-    <row r="980" spans="1:6" ht="15.75" customHeight="1">
+    <row r="980" spans="1:5" ht="15.75" customHeight="1">
       <c r="A980" s="45" t="s">
         <v>162</v>
       </c>
@@ -18245,7 +18264,7 @@
         <v>39814</v>
       </c>
     </row>
-    <row r="981" spans="1:6" ht="15.75" customHeight="1">
+    <row r="981" spans="1:5" ht="15.75" customHeight="1">
       <c r="A981" s="45" t="s">
         <v>162</v>
       </c>
@@ -18260,7 +18279,7 @@
       </c>
       <c r="E981" s="48"/>
     </row>
-    <row r="982" spans="1:6" ht="15.75" customHeight="1">
+    <row r="982" spans="1:5" ht="15.75" customHeight="1">
       <c r="A982" s="45" t="s">
         <v>162</v>
       </c>
@@ -18277,7 +18296,7 @@
         <v>40909</v>
       </c>
     </row>
-    <row r="983" spans="1:6" ht="15.75" customHeight="1">
+    <row r="983" spans="1:5" ht="15.75" customHeight="1">
       <c r="A983" s="45" t="s">
         <v>162</v>
       </c>
@@ -18292,7 +18311,7 @@
       </c>
       <c r="E983" s="48"/>
     </row>
-    <row r="984" spans="1:6" ht="15.75" customHeight="1">
+    <row r="984" spans="1:5" ht="15.75" customHeight="1">
       <c r="A984" s="45" t="s">
         <v>162</v>
       </c>
@@ -18309,7 +18328,7 @@
         <v>39448</v>
       </c>
     </row>
-    <row r="985" spans="1:6" ht="15.75" customHeight="1">
+    <row r="985" spans="1:5" ht="15.75" customHeight="1">
       <c r="A985" s="45" t="s">
         <v>162</v>
       </c>
@@ -18324,7 +18343,7 @@
       </c>
       <c r="E985" s="48"/>
     </row>
-    <row r="986" spans="1:6" ht="15.75" customHeight="1">
+    <row r="986" spans="1:5" ht="15.75" customHeight="1">
       <c r="A986" s="53" t="s">
         <v>162</v>
       </c>
@@ -18341,7 +18360,7 @@
         <v>42736</v>
       </c>
     </row>
-    <row r="987" spans="1:6" ht="15.75" customHeight="1">
+    <row r="987" spans="1:5" ht="15.75" customHeight="1">
       <c r="A987" s="54" t="s">
         <v>5</v>
       </c>
@@ -18355,12 +18374,8 @@
         <v>12</v>
       </c>
       <c r="E987" s="57"/>
-      <c r="F987">
-        <f>COUNTIF(D987:D1183, "Yes")</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="988" spans="1:6" ht="15.75" customHeight="1">
+    </row>
+    <row r="988" spans="1:5" ht="15.75" customHeight="1">
       <c r="A988" s="54" t="s">
         <v>5</v>
       </c>
@@ -18377,7 +18392,7 @@
         <v>41275</v>
       </c>
     </row>
-    <row r="989" spans="1:6" ht="15.75" customHeight="1">
+    <row r="989" spans="1:5" ht="15.75" customHeight="1">
       <c r="A989" s="54" t="s">
         <v>5</v>
       </c>
@@ -18392,7 +18407,7 @@
       </c>
       <c r="E989" s="57"/>
     </row>
-    <row r="990" spans="1:6" ht="15.75" customHeight="1">
+    <row r="990" spans="1:5" ht="15.75" customHeight="1">
       <c r="A990" s="54" t="s">
         <v>5</v>
       </c>
@@ -18407,7 +18422,7 @@
       </c>
       <c r="E990" s="57"/>
     </row>
-    <row r="991" spans="1:6" ht="15.75" customHeight="1">
+    <row r="991" spans="1:5" ht="15.75" customHeight="1">
       <c r="A991" s="54" t="s">
         <v>5</v>
       </c>
@@ -18422,7 +18437,7 @@
       </c>
       <c r="E991" s="57"/>
     </row>
-    <row r="992" spans="1:6" ht="15.75" customHeight="1">
+    <row r="992" spans="1:5" ht="15.75" customHeight="1">
       <c r="A992" s="54" t="s">
         <v>5</v>
       </c>
@@ -21473,7 +21488,7 @@
       </c>
       <c r="E1184" s="66"/>
     </row>
-    <row r="1185" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1185" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1185" s="63" t="s">
         <v>5</v>
       </c>
@@ -21490,7 +21505,7 @@
         <v>43101</v>
       </c>
     </row>
-    <row r="1186" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1186" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1186" s="63" t="s">
         <v>5</v>
       </c>
@@ -21505,7 +21520,7 @@
       </c>
       <c r="E1186" s="66"/>
     </row>
-    <row r="1187" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1187" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1187" s="63" t="s">
         <v>5</v>
       </c>
@@ -21520,7 +21535,7 @@
       </c>
       <c r="E1187" s="66"/>
     </row>
-    <row r="1188" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1188" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1188" s="63" t="s">
         <v>5</v>
       </c>
@@ -21535,7 +21550,7 @@
       </c>
       <c r="E1188" s="66"/>
     </row>
-    <row r="1189" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1189" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1189" s="63" t="s">
         <v>5</v>
       </c>
@@ -21552,7 +21567,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="1190" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1190" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1190" s="63" t="s">
         <v>5</v>
       </c>
@@ -21569,7 +21584,7 @@
         <v>42370</v>
       </c>
     </row>
-    <row r="1191" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1191" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1191" s="63" t="s">
         <v>5</v>
       </c>
@@ -21584,7 +21599,7 @@
       </c>
       <c r="E1191" s="66"/>
     </row>
-    <row r="1192" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1192" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1192" s="63" t="s">
         <v>5</v>
       </c>
@@ -21601,7 +21616,7 @@
         <v>43831</v>
       </c>
     </row>
-    <row r="1193" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1193" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1193" s="63" t="s">
         <v>5</v>
       </c>
@@ -21616,7 +21631,7 @@
       </c>
       <c r="E1193" s="66"/>
     </row>
-    <row r="1194" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1194" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1194" s="63" t="s">
         <v>5</v>
       </c>
@@ -21633,7 +21648,7 @@
         <v>39814</v>
       </c>
     </row>
-    <row r="1195" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1195" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1195" s="63" t="s">
         <v>5</v>
       </c>
@@ -21647,12 +21662,8 @@
         <v>12</v>
       </c>
       <c r="E1195" s="66"/>
-      <c r="F1195">
-        <f>COUNTIF(D1184:D1380, "Yes")</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="1196" spans="1:6" ht="15.75" customHeight="1">
+    </row>
+    <row r="1196" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1196" s="63" t="s">
         <v>5</v>
       </c>
@@ -21667,7 +21678,7 @@
       </c>
       <c r="E1196" s="66"/>
     </row>
-    <row r="1197" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1197" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1197" s="63" t="s">
         <v>5</v>
       </c>
@@ -21682,7 +21693,7 @@
       </c>
       <c r="E1197" s="66"/>
     </row>
-    <row r="1198" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1198" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1198" s="63" t="s">
         <v>5</v>
       </c>
@@ -21699,7 +21710,7 @@
         <v>40909</v>
       </c>
     </row>
-    <row r="1199" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1199" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1199" s="63" t="s">
         <v>5</v>
       </c>
@@ -21714,7 +21725,7 @@
       </c>
       <c r="E1199" s="66"/>
     </row>
-    <row r="1200" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1200" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1200" s="63" t="s">
         <v>5</v>
       </c>
@@ -24507,7 +24518,7 @@
       </c>
       <c r="E1376" s="66"/>
     </row>
-    <row r="1377" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1377" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1377" s="63" t="s">
         <v>162</v>
       </c>
@@ -24522,7 +24533,7 @@
       </c>
       <c r="E1377" s="66"/>
     </row>
-    <row r="1378" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1378" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1378" s="63" t="s">
         <v>162</v>
       </c>
@@ -24537,7 +24548,7 @@
       </c>
       <c r="E1378" s="66"/>
     </row>
-    <row r="1379" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1379" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1379" s="63" t="s">
         <v>162</v>
       </c>
@@ -24552,7 +24563,7 @@
       </c>
       <c r="E1379" s="66"/>
     </row>
-    <row r="1380" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1380" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1380" s="71" t="s">
         <v>162</v>
       </c>
@@ -24567,7 +24578,7 @@
       </c>
       <c r="E1380" s="66"/>
     </row>
-    <row r="1381" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1381" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1381" s="72" t="s">
         <v>5</v>
       </c>
@@ -24581,12 +24592,8 @@
         <v>12</v>
       </c>
       <c r="E1381" s="75"/>
-      <c r="F1381">
-        <f>COUNTIF(D1381:D1577, "Yes")</f>
-        <v>89</v>
-      </c>
-    </row>
-    <row r="1382" spans="1:6" ht="15.75" customHeight="1">
+    </row>
+    <row r="1382" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1382" s="72" t="s">
         <v>5</v>
       </c>
@@ -24603,7 +24610,7 @@
         <v>36161</v>
       </c>
     </row>
-    <row r="1383" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1383" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1383" s="72" t="s">
         <v>5</v>
       </c>
@@ -24618,7 +24625,7 @@
       </c>
       <c r="E1383" s="75"/>
     </row>
-    <row r="1384" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1384" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1384" s="72" t="s">
         <v>5</v>
       </c>
@@ -24633,7 +24640,7 @@
       </c>
       <c r="E1384" s="75"/>
     </row>
-    <row r="1385" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1385" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1385" s="72" t="s">
         <v>5</v>
       </c>
@@ -24648,7 +24655,7 @@
       </c>
       <c r="E1385" s="75"/>
     </row>
-    <row r="1386" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1386" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1386" s="72" t="s">
         <v>5</v>
       </c>
@@ -24665,7 +24672,7 @@
         <v>36526</v>
       </c>
     </row>
-    <row r="1387" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1387" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1387" s="72" t="s">
         <v>5</v>
       </c>
@@ -24680,7 +24687,7 @@
       </c>
       <c r="E1387" s="75"/>
     </row>
-    <row r="1388" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1388" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1388" s="72" t="s">
         <v>5</v>
       </c>
@@ -24697,7 +24704,7 @@
         <v>36161</v>
       </c>
     </row>
-    <row r="1389" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1389" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1389" s="72" t="s">
         <v>5</v>
       </c>
@@ -24714,7 +24721,7 @@
         <v>40909</v>
       </c>
     </row>
-    <row r="1390" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1390" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1390" s="72" t="s">
         <v>5</v>
       </c>
@@ -24731,7 +24738,7 @@
         <v>36892</v>
       </c>
     </row>
-    <row r="1391" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1391" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1391" s="72" t="s">
         <v>5</v>
       </c>
@@ -24748,7 +24755,7 @@
         <v>36161</v>
       </c>
     </row>
-    <row r="1392" spans="1:6" ht="15.75" customHeight="1">
+    <row r="1392" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1392" s="72" t="s">
         <v>5</v>
       </c>
@@ -28751,7 +28758,7 @@
       <c r="B1" s="87"/>
     </row>
     <row r="2" spans="1:2" ht="26">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="146" t="s">
         <v>223</v>
       </c>
       <c r="B2" s="88" t="s">
@@ -28759,61 +28766,61 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="60">
-      <c r="A3" s="144"/>
+      <c r="A3" s="147"/>
       <c r="B3" s="89" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.5">
-      <c r="A4" s="144"/>
+      <c r="A4" s="147"/>
       <c r="B4" s="89"/>
     </row>
     <row r="5" spans="1:2" ht="14.5">
-      <c r="A5" s="144"/>
+      <c r="A5" s="147"/>
       <c r="B5" s="89" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.5">
-      <c r="A6" s="144"/>
+      <c r="A6" s="147"/>
       <c r="B6" s="90" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.5">
-      <c r="A7" s="144"/>
+      <c r="A7" s="147"/>
       <c r="B7" s="90" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.5">
-      <c r="A8" s="144"/>
+      <c r="A8" s="147"/>
       <c r="B8" s="90" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.5">
-      <c r="A9" s="144"/>
+      <c r="A9" s="147"/>
       <c r="B9" s="90" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.5">
-      <c r="A10" s="144"/>
+      <c r="A10" s="147"/>
       <c r="B10" s="89"/>
     </row>
     <row r="11" spans="1:2" ht="14.5">
-      <c r="A11" s="144"/>
+      <c r="A11" s="147"/>
       <c r="B11" s="91" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.5">
-      <c r="A12" s="142"/>
+      <c r="A12" s="145"/>
       <c r="B12" s="92"/>
     </row>
     <row r="13" spans="1:2" ht="64">
-      <c r="A13" s="143" t="s">
+      <c r="A13" s="146" t="s">
         <v>232</v>
       </c>
       <c r="B13" s="89" t="s">
@@ -28821,33 +28828,33 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="24">
-      <c r="A14" s="144"/>
+      <c r="A14" s="147"/>
       <c r="B14" s="89" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.5">
-      <c r="A15" s="144"/>
+      <c r="A15" s="147"/>
       <c r="B15" s="93" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.5">
-      <c r="A16" s="144"/>
+      <c r="A16" s="147"/>
       <c r="B16" s="89"/>
     </row>
     <row r="17" spans="1:2" ht="14.5">
-      <c r="A17" s="144"/>
+      <c r="A17" s="147"/>
       <c r="B17" s="91" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.5">
-      <c r="A18" s="142"/>
+      <c r="A18" s="145"/>
       <c r="B18" s="92"/>
     </row>
     <row r="19" spans="1:2" ht="36">
-      <c r="A19" s="143" t="s">
+      <c r="A19" s="146" t="s">
         <v>237</v>
       </c>
       <c r="B19" s="89" t="s">
@@ -28855,39 +28862,39 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="24">
-      <c r="A20" s="144"/>
+      <c r="A20" s="147"/>
       <c r="B20" s="94" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A21" s="144"/>
+      <c r="A21" s="147"/>
       <c r="B21" s="89" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A22" s="144"/>
+      <c r="A22" s="147"/>
       <c r="B22" s="93" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A23" s="144"/>
+      <c r="A23" s="147"/>
       <c r="B23" s="89"/>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A24" s="144"/>
+      <c r="A24" s="147"/>
       <c r="B24" s="91" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A25" s="142"/>
+      <c r="A25" s="145"/>
       <c r="B25" s="92"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A26" s="143" t="s">
+      <c r="A26" s="146" t="s">
         <v>243</v>
       </c>
       <c r="B26" s="89" t="s">
@@ -28895,17 +28902,17 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A27" s="144"/>
+      <c r="A27" s="147"/>
       <c r="B27" s="89" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A28" s="142"/>
+      <c r="A28" s="145"/>
       <c r="B28" s="92"/>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A29" s="143" t="s">
+      <c r="A29" s="146" t="s">
         <v>246</v>
       </c>
       <c r="B29" s="89" t="s">
@@ -28913,27 +28920,27 @@
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A30" s="144"/>
+      <c r="A30" s="147"/>
       <c r="B30" s="89" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A31" s="144"/>
+      <c r="A31" s="147"/>
       <c r="B31" s="89"/>
     </row>
     <row r="32" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A32" s="144"/>
+      <c r="A32" s="147"/>
       <c r="B32" s="91" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33" s="142"/>
+      <c r="A33" s="145"/>
       <c r="B33" s="92"/>
     </row>
     <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34" s="143" t="s">
+      <c r="A34" s="146" t="s">
         <v>250</v>
       </c>
       <c r="B34" s="89" t="s">
@@ -28941,33 +28948,33 @@
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35" s="144"/>
+      <c r="A35" s="147"/>
       <c r="B35" s="89" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A36" s="144"/>
+      <c r="A36" s="147"/>
       <c r="B36" s="89" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A37" s="144"/>
+      <c r="A37" s="147"/>
       <c r="B37" s="89"/>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A38" s="144"/>
+      <c r="A38" s="147"/>
       <c r="B38" s="91" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A39" s="142"/>
+      <c r="A39" s="145"/>
       <c r="B39" s="92"/>
     </row>
     <row r="40" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A40" s="143" t="s">
+      <c r="A40" s="146" t="s">
         <v>255</v>
       </c>
       <c r="B40" s="89" t="s">
@@ -28975,17 +28982,17 @@
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A41" s="144"/>
+      <c r="A41" s="147"/>
       <c r="B41" s="89" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A42" s="142"/>
+      <c r="A42" s="145"/>
       <c r="B42" s="92"/>
     </row>
     <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43" s="143" t="s">
+      <c r="A43" s="146" t="s">
         <v>258</v>
       </c>
       <c r="B43" s="94" t="s">
@@ -28993,33 +29000,33 @@
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44" s="144"/>
+      <c r="A44" s="147"/>
       <c r="B44" s="89"/>
     </row>
     <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45" s="144"/>
+      <c r="A45" s="147"/>
       <c r="B45" s="89" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A46" s="142"/>
+      <c r="A46" s="145"/>
       <c r="B46" s="92"/>
     </row>
     <row r="47" spans="1:2" ht="27" customHeight="1">
-      <c r="A47" s="143" t="s">
+      <c r="A47" s="146" t="s">
         <v>261</v>
       </c>
-      <c r="B47" s="141" t="s">
+      <c r="B47" s="144" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A48" s="142"/>
-      <c r="B48" s="142"/>
+      <c r="A48" s="145"/>
+      <c r="B48" s="145"/>
     </row>
     <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49" s="143" t="s">
+      <c r="A49" s="146" t="s">
         <v>263</v>
       </c>
       <c r="B49" s="89" t="s">
@@ -29027,33 +29034,33 @@
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A50" s="144"/>
+      <c r="A50" s="147"/>
       <c r="B50" s="89" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A51" s="144"/>
+      <c r="A51" s="147"/>
       <c r="B51" s="89" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A52" s="144"/>
+      <c r="A52" s="147"/>
       <c r="B52" s="89"/>
     </row>
     <row r="53" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A53" s="144"/>
+      <c r="A53" s="147"/>
       <c r="B53" s="89" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A54" s="142"/>
+      <c r="A54" s="145"/>
       <c r="B54" s="92"/>
     </row>
     <row r="55" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A55" s="143" t="s">
+      <c r="A55" s="146" t="s">
         <v>268</v>
       </c>
       <c r="B55" s="89" t="s">
@@ -29061,21 +29068,21 @@
       </c>
     </row>
     <row r="56" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A56" s="144"/>
+      <c r="A56" s="147"/>
       <c r="B56" s="89"/>
     </row>
     <row r="57" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A57" s="144"/>
+      <c r="A57" s="147"/>
       <c r="B57" s="91" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A58" s="142"/>
+      <c r="A58" s="145"/>
       <c r="B58" s="92"/>
     </row>
     <row r="59" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A59" s="143" t="s">
+      <c r="A59" s="146" t="s">
         <v>271</v>
       </c>
       <c r="B59" s="89" t="s">
@@ -29083,17 +29090,17 @@
       </c>
     </row>
     <row r="60" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A60" s="144"/>
+      <c r="A60" s="147"/>
       <c r="B60" s="89" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A61" s="142"/>
+      <c r="A61" s="145"/>
       <c r="B61" s="92"/>
     </row>
     <row r="62" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A62" s="143" t="s">
+      <c r="A62" s="146" t="s">
         <v>274</v>
       </c>
       <c r="B62" s="89" t="s">
@@ -29101,27 +29108,27 @@
       </c>
     </row>
     <row r="63" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A63" s="144"/>
+      <c r="A63" s="147"/>
       <c r="B63" s="89" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A64" s="144"/>
+      <c r="A64" s="147"/>
       <c r="B64" s="89"/>
     </row>
     <row r="65" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A65" s="144"/>
+      <c r="A65" s="147"/>
       <c r="B65" s="91" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A66" s="142"/>
+      <c r="A66" s="145"/>
       <c r="B66" s="92"/>
     </row>
     <row r="67" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A67" s="143" t="s">
+      <c r="A67" s="146" t="s">
         <v>278</v>
       </c>
       <c r="B67" s="95" t="s">
@@ -29129,17 +29136,17 @@
       </c>
     </row>
     <row r="68" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A68" s="144"/>
+      <c r="A68" s="147"/>
       <c r="B68" s="95"/>
     </row>
     <row r="69" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A69" s="144"/>
+      <c r="A69" s="147"/>
       <c r="B69" s="91" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A70" s="142"/>
+      <c r="A70" s="145"/>
       <c r="B70" s="96"/>
     </row>
     <row r="71" spans="1:2" ht="15.75" customHeight="1">
